--- a/assets/template.xlsx
+++ b/assets/template.xlsx
@@ -377,7 +377,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1000125" cy="1000125"/>
+    <ext cx="850000" cy="850000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="02aab8ca-7c7d-4a6d-9e43-7953b66bb572"/>
@@ -407,7 +407,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1000125" cy="1000125"/>
+    <ext cx="850000" cy="850000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="6c972ded-b128-4370-ab83-ca805db3d146"/>
@@ -647,7 +647,7 @@
     <col width="5" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="10" customHeight="1">
+    <row r="1" ht="7.2" customHeight="1">
       <c r="A1" s="4" t="n"/>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
@@ -660,17 +660,13 @@
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="5" t="n"/>
     </row>
-    <row r="2" ht="27" customHeight="1">
+    <row r="2" ht="19.44" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
-        <is>
-          <t>公司名称</t>
-        </is>
-      </c>
+      <c r="B2" s="12" t="n"/>
       <c r="C2" s="15" t="n"/>
       <c r="D2" s="43" t="n"/>
       <c r="E2" s="43" t="n"/>
@@ -685,14 +681,14 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="27" customHeight="1">
+    <row r="3" ht="19.44" customHeight="1">
       <c r="A3" s="4" t="n"/>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="12" t="n"/>
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>地址：</t>
         </is>
       </c>
-      <c r="C3" s="15" t="n"/>
       <c r="D3" s="43" t="n"/>
       <c r="E3" s="43" t="n"/>
       <c r="F3" s="43" t="n"/>
@@ -702,18 +698,18 @@
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="5" t="n"/>
     </row>
-    <row r="4" ht="27" customHeight="1">
+    <row r="4" ht="19.44" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="12" t="n"/>
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>电话：</t>
         </is>
       </c>
-      <c r="C4" s="15" t="n"/>
       <c r="D4" s="43" t="n"/>
       <c r="E4" s="12" t="inlineStr">
         <is>
@@ -731,14 +727,14 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="27" customHeight="1">
+    <row r="5" ht="19.44" customHeight="1">
       <c r="A5" s="4" t="n"/>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>QQ / 其他联系方式：</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="n"/>
+      <c r="B5" s="12" t="n"/>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>QQ：</t>
+        </is>
+      </c>
       <c r="D5" s="43" t="n"/>
       <c r="E5" s="43" t="n"/>
       <c r="F5" s="43" t="n"/>
@@ -748,7 +744,7 @@
       <c r="J5" s="2" t="n"/>
       <c r="K5" s="5" t="n"/>
     </row>
-    <row r="6" ht="24" customHeight="1">
+    <row r="6" ht="17.28" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>●</t>
@@ -777,7 +773,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="36" customHeight="1">
+    <row r="7" ht="25.92" customHeight="1">
       <c r="A7" s="4" t="n"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -794,7 +790,7 @@
       <c r="J7" s="43" t="n"/>
       <c r="K7" s="5" t="n"/>
     </row>
-    <row r="8" ht="28" customHeight="1">
+    <row r="8" ht="20.16" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>●</t>
@@ -827,7 +823,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1">
+    <row r="9" ht="20.16" customHeight="1">
       <c r="A9" s="4" t="n"/>
       <c r="B9" s="12" t="inlineStr">
         <is>
@@ -852,7 +848,7 @@
       <c r="J9" s="2" t="n"/>
       <c r="K9" s="5" t="n"/>
     </row>
-    <row r="10" ht="28" customHeight="1">
+    <row r="10" ht="20.16" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>●</t>
@@ -905,7 +901,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="31" customHeight="1">
+    <row r="11" ht="22.32" customHeight="1">
       <c r="A11" s="4" t="n"/>
       <c r="B11" s="26" t="n"/>
       <c r="C11" s="2" t="n"/>
@@ -925,7 +921,7 @@
       </c>
       <c r="K11" s="5" t="n"/>
     </row>
-    <row r="12" ht="31" customHeight="1">
+    <row r="12" ht="22.32" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>●</t>
@@ -953,7 +949,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="31" customHeight="1">
+    <row r="13" ht="22.32" customHeight="1">
       <c r="A13" s="4" t="n"/>
       <c r="B13" s="26" t="n"/>
       <c r="C13" s="2" t="n"/>
@@ -973,7 +969,7 @@
       </c>
       <c r="K13" s="5" t="n"/>
     </row>
-    <row r="14" ht="31" customHeight="1">
+    <row r="14" ht="22.32" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>●</t>
@@ -1001,7 +997,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="31" customHeight="1">
+    <row r="15" ht="22.32" customHeight="1">
       <c r="A15" s="4" t="n"/>
       <c r="B15" s="26" t="n"/>
       <c r="C15" s="2" t="n"/>
@@ -1021,7 +1017,7 @@
       </c>
       <c r="K15" s="5" t="n"/>
     </row>
-    <row r="16" ht="31" customHeight="1">
+    <row r="16" ht="22.32" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>●</t>
@@ -1049,7 +1045,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="31" customHeight="1">
+    <row r="17" ht="22.32" customHeight="1">
       <c r="A17" s="4" t="n"/>
       <c r="B17" s="17" t="inlineStr">
         <is>
@@ -1077,7 +1073,7 @@
       </c>
       <c r="K17" s="5" t="n"/>
     </row>
-    <row r="18" ht="32" customHeight="1">
+    <row r="18" ht="23.04" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>●</t>
@@ -1106,7 +1102,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="8" customHeight="1">
+    <row r="19" ht="5.76" customHeight="1">
       <c r="A19" s="4" t="n"/>
       <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="n"/>
@@ -1123,7 +1119,7 @@
       </c>
       <c r="K19" s="5" t="n"/>
     </row>
-    <row r="20" ht="26" customHeight="1">
+    <row r="20" ht="18.72" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
           <t>●</t>
@@ -1146,7 +1142,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="26" customHeight="1">
+    <row r="21" ht="18.72" customHeight="1">
       <c r="A21" s="4" t="n"/>
       <c r="B21" s="12" t="inlineStr">
         <is>
@@ -1167,7 +1163,7 @@
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="5" t="n"/>
     </row>
-    <row r="22" ht="11" customHeight="1">
+    <row r="22" ht="7.92" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
           <t>●</t>
@@ -1188,7 +1184,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="28" customHeight="1">
+    <row r="23" ht="20.16" customHeight="1">
       <c r="A23" s="4" t="n"/>
       <c r="B23" s="41" t="n"/>
       <c r="C23" s="43" t="n"/>
@@ -1207,7 +1203,7 @@
       <c r="J23" s="2" t="n"/>
       <c r="K23" s="5" t="n"/>
     </row>
-    <row r="24" ht="20" customHeight="1">
+    <row r="24" ht="14.4" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>●</t>
@@ -1259,7 +1255,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.12" right="0.12" top="0.12" bottom="0.12" header="0" footer="0"/>
-  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup paperWidth="140mm" paperHeight="241mm" orientation="landscape" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>